--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107422341</v>
+        <v>107422342</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441752.3462961138</v>
+        <v>441821</v>
       </c>
       <c r="R2" t="n">
-        <v>6954183.073221833</v>
+        <v>6954192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107422340</v>
+        <v>107422341</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441691.5973116182</v>
+        <v>441752</v>
       </c>
       <c r="R3" t="n">
-        <v>6954178.181152196</v>
+        <v>6954183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,21 +840,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,11 +853,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107422344</v>
+        <v>107422340</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441747.6431724247</v>
+        <v>441691</v>
       </c>
       <c r="R4" t="n">
-        <v>6954541.089845749</v>
+        <v>6954178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,21 +937,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +953,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>silverved av tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,12 +974,7 @@
         <v>107422346</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441747.6431724247</v>
+        <v>441748</v>
       </c>
       <c r="R5" t="n">
-        <v>6954541.089845749</v>
+        <v>6954541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1039,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1076,7 @@
         <v>107422338</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441691.5648571769</v>
+        <v>441691</v>
       </c>
       <c r="R6" t="n">
-        <v>6954176.3460658</v>
+        <v>6954177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1141,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1172,210 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107422343</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>441821</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6954190</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107422344</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>441748</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6954541</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422346</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422338</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422343</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,8 +1411,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422344</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107422342</v>
+        <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441821</v>
+        <v>441725</v>
       </c>
       <c r="R2" t="n">
-        <v>6954192</v>
+        <v>6954272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422342</t>
+          <t>https://artportalen.se/Sighting/135784560</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107422341</v>
+        <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>93209</v>
+        <v>81423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441752</v>
+        <v>441817</v>
       </c>
       <c r="R3" t="n">
-        <v>6954183</v>
+        <v>6954340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422341</t>
+          <t>https://artportalen.se/Sighting/135784565</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107422340</v>
+        <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>91069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441691</v>
+        <v>441717</v>
       </c>
       <c r="R4" t="n">
-        <v>6954178</v>
+        <v>6954272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,36 +965,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422340</t>
+          <t>https://artportalen.se/Sighting/135784562</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107422346</v>
+        <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>79085</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441748</v>
+        <v>441724</v>
       </c>
       <c r="R5" t="n">
-        <v>6954541</v>
+        <v>6954270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,36 +1067,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422346</t>
+          <t>https://artportalen.se/Sighting/135784561</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107422338</v>
+        <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>79917</v>
+        <v>93339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441691</v>
+        <v>441749</v>
       </c>
       <c r="R6" t="n">
-        <v>6954177</v>
+        <v>6954298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,36 +1169,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422338</t>
+          <t>https://artportalen.se/Sighting/135784563</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107422343</v>
+        <v>107422342</v>
       </c>
       <c r="B7" t="n">
-        <v>79917</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,7 +1228,7 @@
         <v>441821</v>
       </c>
       <c r="R7" t="n">
-        <v>6954190</v>
+        <v>6954192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,11 +1272,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1306,16 +1286,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422343</t>
+          <t>https://artportalen.se/Sighting/107422342</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107422344</v>
+        <v>107422341</v>
       </c>
       <c r="B8" t="n">
-        <v>79917</v>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441748</v>
+        <v>441752</v>
       </c>
       <c r="R8" t="n">
-        <v>6954541</v>
+        <v>6954183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,11 +1374,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1413,7 +1388,1052 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/107422341</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135784566</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>441847</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6954410</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784566</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>107422340</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>441691</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6954178</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422340</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784559</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>441725</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6954272</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135784558</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>441669</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6954226</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784558</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135784564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>441817</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6954342</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784564</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107422346</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>441748</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6954541</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422346</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107422338</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>441691</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6954177</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422338</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>107422343</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>441821</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6954190</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422343</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>107422344</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>441748</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6954541</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/107422344</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135784557</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>441701</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6954161</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784557</t>
         </is>
       </c>
     </row>
@@ -1426,6 +2446,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784560</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784565</v>
       </c>
       <c r="B3" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784566</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135784559</v>
       </c>
       <c r="B11" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>135784558</v>
       </c>
       <c r="B12" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>135784564</v>
       </c>
       <c r="B13" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135784557</v>
       </c>
       <c r="B18" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25871-2025 artfynd.xlsx
+++ b/artfynd/A 25871-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135784562</v>
       </c>
       <c r="B4" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784561</v>
       </c>
       <c r="B5" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784563</v>
       </c>
       <c r="B6" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
